--- a/static/assets/LastUpdatedWithPredictions.xlsx
+++ b/static/assets/LastUpdatedWithPredictions.xlsx
@@ -18889,28 +18889,28 @@
         <v>537</v>
       </c>
       <c r="B529">
-        <v>1.026573151777872</v>
+        <v>1.025325869854519</v>
       </c>
       <c r="C529">
-        <v>0.6185959320803529</v>
+        <v>0.6186157200557788</v>
       </c>
       <c r="D529">
-        <v>28.72867808787964</v>
+        <v>28.69519774291497</v>
       </c>
       <c r="E529">
-        <v>68701.77</v>
+        <v>68629.9599760374</v>
       </c>
       <c r="F529">
-        <v>0.5333</v>
+        <v>0.5243</v>
       </c>
       <c r="G529">
-        <v>22.02135163</v>
+        <v>21.76869686</v>
       </c>
       <c r="H529">
         <v>0.89570088967656</v>
       </c>
       <c r="I529">
-        <v>-1.361275679537277</v>
+        <v>-0.1365282441126214</v>
       </c>
       <c r="J529">
         <v>0.3104479610919952</v>

--- a/static/assets/LastUpdatedWithPredictions.xlsx
+++ b/static/assets/LastUpdatedWithPredictions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="540">
   <si>
     <t>date</t>
   </si>
@@ -1628,6 +1628,12 @@
   </si>
   <si>
     <t>2026-02-09</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
   </si>
 </sst>
 </file>
@@ -1985,7 +1991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J529"/>
+  <dimension ref="A1:J531"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -18916,6 +18922,70 @@
         <v>0.3104479610919952</v>
       </c>
     </row>
+    <row r="530" spans="1:10">
+      <c r="A530" t="s">
+        <v>538</v>
+      </c>
+      <c r="B530">
+        <v>1.008465917943873</v>
+      </c>
+      <c r="C530">
+        <v>0.6391141549524367</v>
+      </c>
+      <c r="D530">
+        <v>28.16362773866994</v>
+      </c>
+      <c r="E530">
+        <v>67550.0240768556</v>
+      </c>
+      <c r="F530">
+        <v>0.4713</v>
+      </c>
+      <c r="G530">
+        <v>19.81164541</v>
+      </c>
+      <c r="H530">
+        <v>1.023559664283583</v>
+      </c>
+      <c r="I530">
+        <v>-0.3276290156025374</v>
+      </c>
+      <c r="J530">
+        <v>0.2898770570755005</v>
+      </c>
+    </row>
+    <row r="531" spans="1:10">
+      <c r="A531" t="s">
+        <v>539</v>
+      </c>
+      <c r="B531">
+        <v>0.9565927406904376</v>
+      </c>
+      <c r="C531">
+        <v>0.6589345494038351</v>
+      </c>
+      <c r="D531">
+        <v>26.48662992508103</v>
+      </c>
+      <c r="E531">
+        <v>64122.6</v>
+      </c>
+      <c r="F531">
+        <v>0.355</v>
+      </c>
+      <c r="G531">
+        <v>15.87121624</v>
+      </c>
+      <c r="H531">
+        <v>1.020126259682869</v>
+      </c>
+      <c r="I531">
+        <v>-2.202666083750615</v>
+      </c>
+      <c r="J531">
+        <v>0.2639527320861816</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/static/assets/LastUpdatedWithPredictions.xlsx
+++ b/static/assets/LastUpdatedWithPredictions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="541">
   <si>
     <t>date</t>
   </si>
@@ -1634,6 +1634,9 @@
   </si>
   <si>
     <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
   </si>
 </sst>
 </file>
@@ -1991,7 +1994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J531"/>
+  <dimension ref="A1:J532"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -18959,31 +18962,63 @@
         <v>539</v>
       </c>
       <c r="B531">
-        <v>0.9565927406904376</v>
+        <v>0.9806061220043184</v>
       </c>
       <c r="C531">
-        <v>0.6589345494038351</v>
+        <v>0.6584277324416361</v>
       </c>
       <c r="D531">
-        <v>26.48662992508103</v>
+        <v>27.24924402223559</v>
       </c>
       <c r="E531">
-        <v>64122.6</v>
+        <v>65733.5212597896</v>
       </c>
       <c r="F531">
-        <v>0.355</v>
+        <v>0.4348</v>
       </c>
       <c r="G531">
-        <v>15.87121624</v>
+        <v>19.00632618</v>
       </c>
       <c r="H531">
         <v>1.020126259682869</v>
       </c>
       <c r="I531">
-        <v>-2.202666083750615</v>
+        <v>-0.4157992356869644</v>
       </c>
       <c r="J531">
         <v>0.2639527320861816</v>
+      </c>
+    </row>
+    <row r="532" spans="1:10">
+      <c r="A532" t="s">
+        <v>540</v>
+      </c>
+      <c r="B532">
+        <v>1.018687545728661</v>
+      </c>
+      <c r="C532">
+        <v>0.6757252422537738</v>
+      </c>
+      <c r="D532">
+        <v>30.66852761628543</v>
+      </c>
+      <c r="E532">
+        <v>68295.74000000001</v>
+      </c>
+      <c r="F532">
+        <v>0.502</v>
+      </c>
+      <c r="G532">
+        <v>21.76430238</v>
+      </c>
+      <c r="H532">
+        <v>1.017201621969498</v>
+      </c>
+      <c r="I532">
+        <v>-0.407894154680799</v>
+      </c>
+      <c r="J532">
+        <v>0.2336353808641434</v>
       </c>
     </row>
   </sheetData>

--- a/static/assets/LastUpdatedWithPredictions.xlsx
+++ b/static/assets/LastUpdatedWithPredictions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="542">
   <si>
     <t>date</t>
   </si>
@@ -1637,6 +1637,9 @@
   </si>
   <si>
     <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
   </si>
 </sst>
 </file>
@@ -1994,7 +1997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J532"/>
+  <dimension ref="A1:J533"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -18994,31 +18997,63 @@
         <v>540</v>
       </c>
       <c r="B532">
-        <v>1.018687545728661</v>
+        <v>0.9870493702772729</v>
       </c>
       <c r="C532">
-        <v>0.6757252422537738</v>
+        <v>0.6764201477744798</v>
       </c>
       <c r="D532">
-        <v>30.66852761628543</v>
+        <v>27.90035939903984</v>
       </c>
       <c r="E532">
-        <v>68295.74000000001</v>
+        <v>66202.6978731736</v>
       </c>
       <c r="F532">
-        <v>0.502</v>
+        <v>0.4517</v>
       </c>
       <c r="G532">
-        <v>21.76430238</v>
+        <v>19.19734902</v>
       </c>
       <c r="H532">
-        <v>1.017201621969498</v>
+        <v>1.021075057604597</v>
       </c>
       <c r="I532">
-        <v>-0.407894154680799</v>
+        <v>-0.3713599639914023</v>
       </c>
       <c r="J532">
         <v>0.2336353808641434</v>
+      </c>
+    </row>
+    <row r="533" spans="1:10">
+      <c r="A533" t="s">
+        <v>541</v>
+      </c>
+      <c r="B533">
+        <v>1.039786136803844</v>
+      </c>
+      <c r="C533">
+        <v>0.6966425534876695</v>
+      </c>
+      <c r="D533">
+        <v>32.80651926533788</v>
+      </c>
+      <c r="E533">
+        <v>69756.92999999999</v>
+      </c>
+      <c r="F533">
+        <v>0.4901</v>
+      </c>
+      <c r="G533">
+        <v>20.89028266</v>
+      </c>
+      <c r="H533">
+        <v>1.01801011164104</v>
+      </c>
+      <c r="I533">
+        <v>-0.01399058563303912</v>
+      </c>
+      <c r="J533">
+        <v>0.2005561739206314</v>
       </c>
     </row>
   </sheetData>

--- a/static/assets/LastUpdatedWithPredictions.xlsx
+++ b/static/assets/LastUpdatedWithPredictions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="543">
   <si>
     <t>date</t>
   </si>
@@ -1640,6 +1640,9 @@
   </si>
   <si>
     <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-16</t>
   </si>
 </sst>
 </file>
@@ -1997,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J533"/>
+  <dimension ref="A1:J534"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -19029,31 +19032,63 @@
         <v>541</v>
       </c>
       <c r="B533">
-        <v>1.039786136803844</v>
+        <v>1.082963085798875</v>
       </c>
       <c r="C533">
-        <v>0.6966425534876695</v>
+        <v>0.69560060922075</v>
       </c>
       <c r="D533">
-        <v>32.80651926533788</v>
+        <v>36.40465383079862</v>
       </c>
       <c r="E533">
-        <v>69756.92999999999</v>
+        <v>72712.14619579189</v>
       </c>
       <c r="F533">
-        <v>0.4901</v>
+        <v>0.5858</v>
       </c>
       <c r="G533">
-        <v>20.89028266</v>
+        <v>23.33901612</v>
       </c>
       <c r="H533">
         <v>1.01801011164104</v>
       </c>
       <c r="I533">
-        <v>-0.01399058563303912</v>
+        <v>0.2714736419145547</v>
       </c>
       <c r="J533">
         <v>0.2005561739206314</v>
+      </c>
+    </row>
+    <row r="534" spans="1:10">
+      <c r="A534" t="s">
+        <v>542</v>
+      </c>
+      <c r="B534">
+        <v>1.105816455061559</v>
+      </c>
+      <c r="C534">
+        <v>0.7134131874039986</v>
+      </c>
+      <c r="D534">
+        <v>38.31662014621086</v>
+      </c>
+      <c r="E534">
+        <v>74300.57000000001</v>
+      </c>
+      <c r="F534">
+        <v>0.701</v>
+      </c>
+      <c r="G534">
+        <v>27.52482478</v>
+      </c>
+      <c r="H534">
+        <v>1.015397622421061</v>
+      </c>
+      <c r="I534">
+        <v>0.01163126283620919</v>
+      </c>
+      <c r="J534">
+        <v>0.170338898897171</v>
       </c>
     </row>
   </sheetData>

--- a/static/assets/LastUpdatedWithPredictions.xlsx
+++ b/static/assets/LastUpdatedWithPredictions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="546">
   <si>
     <t>date</t>
   </si>
@@ -1649,6 +1649,9 @@
   </si>
   <si>
     <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
   </si>
 </sst>
 </file>
@@ -2006,7 +2009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J536"/>
+  <dimension ref="A1:J537"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -19161,6 +19164,38 @@
         <v>0.07553667575120926</v>
       </c>
     </row>
+    <row r="537" spans="1:10">
+      <c r="A537" t="s">
+        <v>545</v>
+      </c>
+      <c r="B537">
+        <v>1.038848469601116</v>
+      </c>
+      <c r="C537">
+        <v>0.7609441450091261</v>
+      </c>
+      <c r="D537">
+        <v>37.45164862067018</v>
+      </c>
+      <c r="E537">
+        <v>70087.42</v>
+      </c>
+      <c r="F537">
+        <v>0.5154</v>
+      </c>
+      <c r="G537">
+        <v>22.25125845</v>
+      </c>
+      <c r="H537">
+        <v>0.9936664274471224</v>
+      </c>
+      <c r="I537">
+        <v>-0.3690862872358203</v>
+      </c>
+      <c r="J537">
+        <v>0.05187227204442024</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
